--- a/SoftwareAnalysis/PE/Interviewvragen PXL ShuttleApp.xlsx
+++ b/SoftwareAnalysis/PE/Interviewvragen PXL ShuttleApp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12401891\Documents\2TIN\SoftwareAnalysis\PE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12401259\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3116DB5D-159C-49B3-A522-1B8F144DE6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE08E9C-A87F-4FCD-ABC1-5509FE28FC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="102">
   <si>
     <t>Hoe ervaart u vandaag de interne mobiliteit tussen de PXL-campussen?</t>
   </si>
@@ -193,6 +193,144 @@
   </si>
   <si>
     <t>Bij parkeerproblemen</t>
+  </si>
+  <si>
+    <t>Voorlopig geen problemen mee gehad</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>Voldoende shuttles beschikbaar</t>
+  </si>
+  <si>
+    <t>Als ik ergens strict op tijd moet zijn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Korte afstanden </t>
+  </si>
+  <si>
+    <t>Belangrijk</t>
+  </si>
+  <si>
+    <t>Zodra ik weet dat ik een shuttle nodig ga hebben</t>
+  </si>
+  <si>
+    <t>Flexibel</t>
+  </si>
+  <si>
+    <t>Wel: Vertraging</t>
+  </si>
+  <si>
+    <t>Ja</t>
+  </si>
+  <si>
+    <t>Simpel UI, weinig kliks</t>
+  </si>
+  <si>
+    <t>Kosten besparen</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>Piektijden, bezettingsgraad van shuttles, sieizoensvariaties</t>
+  </si>
+  <si>
+    <t>Belangrijk: optimalisatie van routes en shuttlecapaciteit</t>
+  </si>
+  <si>
+    <t>Real-time of binnen enkele minuten voor kritieke storingen</t>
+  </si>
+  <si>
+    <t>Reserveringen en annuleren van ritten</t>
+  </si>
+  <si>
+    <t>Outlook/PXL App kalender</t>
+  </si>
+  <si>
+    <t>Mogelijkheid om data te koppelen aan andere systemen of apps binnen PXL</t>
+  </si>
+  <si>
+    <t>Reserveringen en gebruikersgegevens</t>
+  </si>
+  <si>
+    <t>Rapporten over gebruik, bezettingsgraad en trends.</t>
+  </si>
+  <si>
+    <t>Mogelijke limieten in het aantal voertuigen of personeel voor ritten</t>
+  </si>
+  <si>
+    <t>Indien de app niet betrouwbaar functioneert of veel klachten oplevert</t>
+  </si>
+  <si>
+    <t>met de bus</t>
+  </si>
+  <si>
+    <t>een dag op voorhand</t>
+  </si>
+  <si>
+    <t>heel belangrijk</t>
+  </si>
+  <si>
+    <t>moelijk om tijdig op de campus te komen</t>
+  </si>
+  <si>
+    <t>bussen die staken</t>
+  </si>
+  <si>
+    <t>een betere verbinding tussen de campussen</t>
+  </si>
+  <si>
+    <t>als ik met snel moet verplaatsen tussen de campussen</t>
+  </si>
+  <si>
+    <t>als de shuttlebus constant te laat is</t>
+  </si>
+  <si>
+    <t>flexibel</t>
+  </si>
+  <si>
+    <t>wel: stakingen, vertraging</t>
+  </si>
+  <si>
+    <t>ja om sneller te zien wannneer ik een shuttle kan pakken</t>
+  </si>
+  <si>
+    <t>duidelijk UI</t>
+  </si>
+  <si>
+    <t>foute informatie</t>
+  </si>
+  <si>
+    <t>makkelijker vervoer</t>
+  </si>
+  <si>
+    <t>bezettingsaantallen, piekmomenten, reservatieaantallen</t>
+  </si>
+  <si>
+    <t>binnen de paar minuten</t>
+  </si>
+  <si>
+    <t>meldingen, reservaties</t>
+  </si>
+  <si>
+    <t>school apps en accounts</t>
+  </si>
+  <si>
+    <t>gebruikersgegevens, resevaties</t>
+  </si>
+  <si>
+    <t>mogelijkheid voor meet routes als er meer gebruikers zijn</t>
+  </si>
+  <si>
+    <t>trends, bezettingsgraad en gebruik</t>
+  </si>
+  <si>
+    <t>de oplossing moet efficiënt zijn</t>
+  </si>
+  <si>
+    <t>als de app en shuttlebussen niet genoeg worden gebruikt</t>
   </si>
 </sst>
 </file>
@@ -676,13 +814,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="79.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="79.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.85546875" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" customWidth="1"/>
+    <col min="6" max="6" width="69.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="5"/>
       <c r="B1" s="6" t="s">
         <v>14</v>
@@ -700,7 +841,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -710,11 +851,15 @@
       <c r="C2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -724,11 +869,15 @@
       <c r="C3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F3" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -738,11 +887,15 @@
       <c r="C4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="9"/>
+      <c r="D4" s="9" t="s">
+        <v>84</v>
+      </c>
       <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F4" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -752,11 +905,15 @@
       <c r="C5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="9"/>
+      <c r="D5" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F5" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -766,11 +923,15 @@
       <c r="C6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>85</v>
+      </c>
       <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F6" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -780,11 +941,15 @@
       <c r="C7" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="9"/>
+      <c r="D7" s="9" t="s">
+        <v>86</v>
+      </c>
       <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -794,11 +959,15 @@
       <c r="C8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="9"/>
+      <c r="D8" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -808,11 +977,15 @@
       <c r="C9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -822,11 +995,15 @@
       <c r="C10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>87</v>
+      </c>
       <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -836,11 +1013,15 @@
       <c r="C11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="9"/>
+      <c r="D11" s="9" t="s">
+        <v>88</v>
+      </c>
       <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -850,11 +1031,15 @@
       <c r="C12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>89</v>
+      </c>
       <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F12" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -864,11 +1049,15 @@
       <c r="C13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="9"/>
+      <c r="D13" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F13" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -878,11 +1067,15 @@
       <c r="C14" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F14" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -892,11 +1085,15 @@
       <c r="C15" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>92</v>
+      </c>
       <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F15" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -904,7 +1101,7 @@
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="6" t="s">
         <v>21</v>
@@ -914,7 +1111,7 @@
       <c r="E17" s="12"/>
       <c r="F17" s="13"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -924,11 +1121,15 @@
       <c r="C18" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="8"/>
+      <c r="D18" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F18" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -938,11 +1139,15 @@
       <c r="C19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="9"/>
+      <c r="D19" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F19" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -952,11 +1157,15 @@
       <c r="C20" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="9"/>
+      <c r="D20" s="9" t="s">
+        <v>94</v>
+      </c>
       <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F20" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -966,11 +1175,15 @@
       <c r="C21" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>95</v>
+      </c>
       <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F21" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -980,11 +1193,15 @@
       <c r="C22" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="9"/>
+      <c r="D22" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F22" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -994,11 +1211,15 @@
       <c r="C23" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -1008,11 +1229,15 @@
       <c r="C24" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="1"/>
       <c r="C25" s="10"/>
@@ -1020,7 +1245,7 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="6" t="s">
         <v>22</v>
@@ -1030,7 +1255,7 @@
       <c r="E26" s="15"/>
       <c r="F26" s="16"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>22</v>
       </c>
@@ -1040,11 +1265,15 @@
       <c r="C27" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="8"/>
+      <c r="D27" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F27" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>23</v>
       </c>
@@ -1054,11 +1283,15 @@
       <c r="C28" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="9"/>
+      <c r="D28" s="9" t="s">
+        <v>99</v>
+      </c>
       <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F28" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>24</v>
       </c>
@@ -1068,11 +1301,15 @@
       <c r="C29" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D29" s="9"/>
+      <c r="D29" s="9" t="s">
+        <v>100</v>
+      </c>
       <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F29" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>25</v>
       </c>
@@ -1082,11 +1319,15 @@
       <c r="C30" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D30" s="9"/>
+      <c r="D30" s="9" t="s">
+        <v>101</v>
+      </c>
       <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F30" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="10"/>
